--- a/output/pdf_financials_xlsx/BRON.xlsx
+++ b/output/pdf_financials_xlsx/BRON.xlsx
@@ -6145,13 +6145,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.010935</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.237575</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.284284</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>1.327794</v>
@@ -7851,19 +7851,19 @@
         <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.31056</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.946114</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.109033</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.271724</v>
+        <v>0.271136</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.389992</v>
       </c>
     </row>
     <row r="119">
@@ -17597,7 +17597,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -18888,7 +18892,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -19969,7 +19977,11 @@
           <t>Exploration and evaluation asset expenditures 5</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -21135,7 +21147,11 @@
           <t>Exploration and evaluation asset expenditures 5</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -22349,7 +22365,11 @@
           <t>Exploration and evaluation asset                                        5 expenditures</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -41186,7 +41206,7 @@
         </is>
       </c>
       <c r="K321" s="5" t="n">
-        <v>2e-06</v>
+        <v>-2e-06</v>
       </c>
       <c r="L321" s="5" t="n">
         <v>-0.29211</v>

--- a/output/pdf_financials_xlsx/BRON.xlsx
+++ b/output/pdf_financials_xlsx/BRON.xlsx
@@ -987,37 +987,37 @@
         <v>0.22599</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.29211</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.288819</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>0.114021</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>0.189231</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>0.221622</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.066715</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.371124</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>0.237759</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>0.194734</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>0.171361</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>0.262433</v>
       </c>
     </row>
     <row r="11">
@@ -1053,22 +1053,22 @@
         <v>-0.22599</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-0.29211</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-0.288819</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>-0.114021</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>-0.189231</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0</v>
+        <v>-0.221622</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>-0.066715</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -2553,16 +2553,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.573353</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.263179</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.281261</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.037403</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.108175</v>
@@ -2571,7 +2571,7 @@
         <v>0.022758</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.064538</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.002772</v>
@@ -2583,7 +2583,7 @@
         <v>0.080524</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.068623</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.496497</v>
@@ -2595,10 +2595,10 @@
         <v>0.02981</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.014699</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.089867</v>
       </c>
     </row>
     <row r="35">
@@ -2673,16 +2673,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.573353</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.263179</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.281261</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.037403</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.108175</v>
@@ -2691,7 +2691,7 @@
         <v>0.022758</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.064538</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.002772</v>
@@ -2703,7 +2703,7 @@
         <v>0.080524</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.068623</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0.496497</v>
@@ -2715,10 +2715,10 @@
         <v>0.02981</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.014699</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.089867</v>
       </c>
     </row>
     <row r="37">
@@ -3393,16 +3393,16 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.6419280000000001</v>
+        <v>0.068575</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.287205</v>
+        <v>0.024026</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.321998</v>
+        <v>0.040737</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.037403</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.011366</v>
@@ -3411,7 +3411,7 @@
         <v>0.001542</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.374404</v>
+        <v>0.309866</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.453286</v>
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.069017</v>
+        <v>0.000394</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.8257679999999999</v>
@@ -3435,10 +3435,10 @@
         <v>0.001114</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.015188</v>
+        <v>0.000489</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.09051099999999999</v>
+        <v>0.000644</v>
       </c>
     </row>
     <row r="49">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16797,7 +16797,11 @@
           <t>Reclamation deposits (note 8)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -18007,7 +18011,11 @@
           <t>Reclamation deposits (note 9)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -18201,7 +18209,11 @@
           <t>Reclamation Deposits (note 9)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -29108,7 +29120,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -30015,7 +30031,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -30074,22 +30090,22 @@
         </is>
       </c>
       <c r="P210" s="5" t="n">
-        <v>-0.066715</v>
+        <v>0.066715</v>
       </c>
       <c r="Q210" s="5" t="n">
-        <v>-0.371124</v>
+        <v>0.371124</v>
       </c>
       <c r="R210" s="5" t="n">
-        <v>-0.237759</v>
+        <v>0.237759</v>
       </c>
       <c r="S210" s="5" t="n">
-        <v>-0.194734</v>
+        <v>0.194734</v>
       </c>
       <c r="T210" s="5" t="n">
-        <v>-0.171361</v>
+        <v>0.171361</v>
       </c>
       <c r="U210" s="5" t="n">
-        <v>-0.262433</v>
+        <v>0.262433</v>
       </c>
     </row>
     <row r="211">
@@ -36637,7 +36653,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -36666,22 +36682,22 @@
         </is>
       </c>
       <c r="J276" s="5" t="n">
-        <v>-0.22599</v>
+        <v>0.22599</v>
       </c>
       <c r="K276" s="5" t="n">
-        <v>-0.29211</v>
+        <v>0.29211</v>
       </c>
       <c r="L276" s="5" t="n">
-        <v>-0.288819</v>
+        <v>0.288819</v>
       </c>
       <c r="M276" s="5" t="n">
-        <v>-0.114021</v>
+        <v>0.114021</v>
       </c>
       <c r="N276" s="5" t="n">
-        <v>-0.189231</v>
+        <v>0.189231</v>
       </c>
       <c r="O276" s="5" t="n">
-        <v>-0.221622</v>
+        <v>0.221622</v>
       </c>
       <c r="P276" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BRON.xlsx
+++ b/output/pdf_financials_xlsx/BRON.xlsx
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.083968</v>
+        <v>-0.083968</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.008</v>
+        <v>-0.008</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1438,10 +1438,10 @@
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.009990000000000001</v>
+        <v>-0.009990000000000001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.018673</v>
+        <v>-0.018673</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0.028663</v>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.096332</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003836</v>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.451978</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.096332</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003836</v>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
@@ -9003,10 +9003,10 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.707749</v>
+        <v>-0.804081</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.015817</v>
+        <v>-0.019653</v>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
@@ -20187,7 +20187,11 @@
           <t>Proceeds from private placement 6</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -22680,7 +22684,11 @@
           <t>Private placements 7</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -23660,7 +23668,11 @@
           <t>Private placements 6,7</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -24573,7 +24585,11 @@
           <t>Share issued for private placement 6</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -25278,7 +25294,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -25379,7 +25399,11 @@
           <t>Proceeds from sale of marketable securities 5</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -25686,7 +25710,11 @@
           <t>Proceeds from private placement 8</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -27310,7 +27338,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -29021,7 +29053,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -30124,7 +30160,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -39360,7 +39400,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -48640,7 +48684,11 @@
           <t>Deferred Income Tax Recovery (note 11)</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -51236,7 +51284,11 @@
           <t>Deferred Income Tax Recovery (note 12)</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
